--- a/Deliverables/Sprint/Soen 341 - agile planning.xlsx
+++ b/Deliverables/Sprint/Soen 341 - agile planning.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\louay\Desktop\LZJCO-SOEN341_Project_W26\Deliverables\Sprint\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1621C30-F2D6-402D-9B70-7BC7A7E9990E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8F16B26-3507-4305-9967-EDA8DF4FA6D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,12 +16,25 @@
     <sheet name="Cover" sheetId="1" r:id="rId1"/>
     <sheet name="Product Backlog" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="63">
   <si>
     <t>Team LZJCO</t>
   </si>
@@ -176,6 +189,75 @@
 Octavian
 Backend:
 Constance</t>
+  </si>
+  <si>
+    <t>User will be able to see his weekly mean plan</t>
+  </si>
+  <si>
+    <t>User will be able to assign meals to the day of the week and its type (breakfast/lunch/dinner/snack)</t>
+  </si>
+  <si>
+    <t>-Deisng the UI for the weekkly meal plan
+-Have the ability to go to the next/previous week
+-Have the week start at Sunday and end on Saturday
+-Upon clicking on the day of the week, Buttons to add, eidt and remove meals from the day will appear</t>
+  </si>
+  <si>
+    <t>-Upon clicking on the add recipe button for a day, get all recipes from the database and assign it to that day
+-Meals should also get a type that will be assigned to them (breakfast/lunch/dinner/snack)</t>
+  </si>
+  <si>
+    <t>User will be able to edit or remove meals from a day</t>
+  </si>
+  <si>
+    <t>-Upon clicking on the remove/edit button, prompt the user to select which recipe of that day they want to remove/edit
+-Remove/edit that specific meal</t>
+  </si>
+  <si>
+    <t>Frontend: 
+Octavian</t>
+  </si>
+  <si>
+    <t>Constance</t>
+  </si>
+  <si>
+    <t>Cedric</t>
+  </si>
+  <si>
+    <t>HIGH: If there's no way to display recipes in a weekly manner, there is also no way to create/edit/remove recipes</t>
+  </si>
+  <si>
+    <t>System will prevent duplicate meal assignments in the same week</t>
+  </si>
+  <si>
+    <t>-Implement duplicate validation logic
+-Check if recipe already exists in same week
+-Prevent overwrite
+-Display error message</t>
+  </si>
+  <si>
+    <t>System will automatically test  every push and pull request made</t>
+  </si>
+  <si>
+    <t>-Write test cases
+-Validate CRUD operations
+-Test duplicate prevention
+-Perform integration testing</t>
+  </si>
+  <si>
+    <t>HIGH: If there is no recipe added, then it is impossible to edit/remove them</t>
+  </si>
+  <si>
+    <t>MEDIUM: User cannot modify weekly plan</t>
+  </si>
+  <si>
+    <t>Zaree</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LOW: It does not affect any other task</t>
+  </si>
+  <si>
+    <t>LOW: It does not affect ay other task</t>
   </si>
 </sst>
 </file>
@@ -338,7 +420,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -387,6 +469,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="7" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -613,13 +698,13 @@
     <col min="3" max="3" width="47.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="3:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="3:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="3:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="C3" s="1"/>
     </row>
     <row r="4" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -627,10 +712,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="3:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="C5" s="1"/>
     </row>
-    <row r="6" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="3:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="C6" s="1"/>
     </row>
     <row r="7" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -638,95 +723,95 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="3:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="C8" s="1"/>
     </row>
-    <row r="9" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="3:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="3:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="3:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="3:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="3:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="3:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="C16" s="1"/>
     </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="C17" s="1"/>
     </row>
-    <row r="18" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="C18" s="1"/>
     </row>
-    <row r="19" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="C19" s="1"/>
     </row>
-    <row r="20" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="C20" s="1"/>
     </row>
-    <row r="21" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="C21" s="1"/>
     </row>
-    <row r="22" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="C22" s="1"/>
     </row>
-    <row r="23" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="C23" s="1"/>
     </row>
-    <row r="24" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="C24" s="1"/>
     </row>
-    <row r="25" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="C25" s="1"/>
     </row>
-    <row r="26" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="C26" s="1"/>
     </row>
-    <row r="27" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="C27" s="1"/>
     </row>
-    <row r="28" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="C28" s="1"/>
     </row>
-    <row r="29" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="C29" s="1"/>
     </row>
-    <row r="30" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="C30" s="1"/>
     </row>
-    <row r="31" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="C31" s="1"/>
     </row>
-    <row r="32" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="C32" s="1"/>
     </row>
-    <row r="33" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="3:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="C33" s="1"/>
     </row>
-    <row r="34" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="3:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="C34" s="1"/>
     </row>
-    <row r="35" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="3:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="C35" s="1"/>
     </row>
-    <row r="36" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="3:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="C36" s="1"/>
     </row>
     <row r="37" spans="3:3" ht="12.75" x14ac:dyDescent="0.2">
@@ -4078,17 +4163,31 @@
       <c r="Y11" s="5"/>
       <c r="Z11" s="5"/>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:26" ht="157.5" x14ac:dyDescent="0.2">
       <c r="A12" s="10">
         <v>8</v>
       </c>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="14"/>
+      <c r="B12" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="12">
+        <v>4</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H12" s="14">
+        <v>46099</v>
+      </c>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>
@@ -4108,17 +4207,31 @@
       <c r="Y12" s="5"/>
       <c r="Z12" s="5"/>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" ht="157.5" x14ac:dyDescent="0.2">
       <c r="A13" s="10">
         <v>9</v>
       </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="14"/>
+      <c r="B13" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="12">
+        <v>6</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="H13" s="14">
+        <v>46101</v>
+      </c>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
       <c r="K13" s="4"/>
@@ -4138,17 +4251,31 @@
       <c r="Y13" s="5"/>
       <c r="Z13" s="5"/>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:26" ht="110.25" x14ac:dyDescent="0.2">
       <c r="A14" s="10">
         <v>10</v>
       </c>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="14"/>
+      <c r="B14" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" s="12">
+        <v>5</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="H14" s="14">
+        <v>46102</v>
+      </c>
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
       <c r="K14" s="4"/>
@@ -4168,17 +4295,31 @@
       <c r="Y14" s="5"/>
       <c r="Z14" s="5"/>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" ht="94.5" x14ac:dyDescent="0.2">
       <c r="A15" s="10">
         <v>11</v>
       </c>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="14"/>
+      <c r="B15" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="12">
+        <v>2</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="H15" s="14">
+        <v>46102</v>
+      </c>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
@@ -4198,17 +4339,31 @@
       <c r="Y15" s="5"/>
       <c r="Z15" s="5"/>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:26" ht="63" x14ac:dyDescent="0.2">
       <c r="A16" s="10">
         <v>12</v>
       </c>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="14"/>
+      <c r="B16" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" s="12">
+        <v>5</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="H16" s="14">
+        <v>46102</v>
+      </c>
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>

--- a/Deliverables/Sprint/Soen 341 - agile planning.xlsx
+++ b/Deliverables/Sprint/Soen 341 - agile planning.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\louay\Desktop\LZJCO-SOEN341_Project_W26\Deliverables\Sprint\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8F16B26-3507-4305-9967-EDA8DF4FA6D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA0F2053-EE94-4EB7-BCCB-C2135C1261F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="66">
   <si>
     <t>Team LZJCO</t>
   </si>
@@ -258,6 +258,17 @@
   </si>
   <si>
     <t>LOW: It does not affect ay other task</t>
+  </si>
+  <si>
+    <t>User will be able to ask for a weekly plan given certain ingrediants</t>
+  </si>
+  <si>
+    <t>-Create API key for LLM
+-Initialize Firebase Functions
+- Manage the LLM-firebase functions pipeline</t>
+  </si>
+  <si>
+    <t>Louay</t>
   </si>
 </sst>
 </file>
@@ -4383,17 +4394,31 @@
       <c r="Y16" s="5"/>
       <c r="Z16" s="5"/>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:26" ht="63" x14ac:dyDescent="0.2">
       <c r="A17" s="10">
         <v>13</v>
       </c>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="14"/>
+      <c r="B17" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17" s="12">
+        <v>6</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="H17" s="14">
+        <v>46102</v>
+      </c>
       <c r="I17" s="4"/>
       <c r="J17" s="4"/>
       <c r="K17" s="4"/>

--- a/Deliverables/Sprint/Soen 341 - agile planning.xlsx
+++ b/Deliverables/Sprint/Soen 341 - agile planning.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\louay\Desktop\LZJCO-SOEN341_Project_W26\Deliverables\Sprint\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA0F2053-EE94-4EB7-BCCB-C2135C1261F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91D59408-85C5-493E-BC55-01E936E30B93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="68">
   <si>
     <t>Team LZJCO</t>
   </si>
@@ -270,6 +270,14 @@
   <si>
     <t>Louay</t>
   </si>
+  <si>
+    <t>user will be able to track his daily calories on the calendar</t>
+  </si>
+  <si>
+    <t>-Update infroamtion sent to firebase to include calories
+-Include daily calorie limit in the user's profile preferences
+-Update recipe UI to include calories</t>
+  </si>
 </sst>
 </file>
 
@@ -279,7 +287,7 @@
     <numFmt numFmtId="164" formatCode="mmm\ d"/>
     <numFmt numFmtId="165" formatCode="mmmm\ d"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -324,8 +332,20 @@
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -350,8 +370,14 @@
         <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -427,11 +453,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -484,6 +534,23 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4438,17 +4505,15 @@
       <c r="Y17" s="5"/>
       <c r="Z17" s="5"/>
     </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A18" s="10">
-        <v>14</v>
-      </c>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="14"/>
+    <row r="18" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A18" s="19"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
       <c r="I18" s="4"/>
       <c r="J18" s="4"/>
       <c r="K18" s="4"/>
@@ -4468,17 +4533,31 @@
       <c r="Y18" s="5"/>
       <c r="Z18" s="5"/>
     </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A19" s="10">
-        <v>15</v>
+    <row r="19" spans="1:26" ht="115.5" x14ac:dyDescent="0.2">
+      <c r="A19" s="20">
+        <v>14</v>
       </c>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="14"/>
+      <c r="B19" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="D19" s="20">
+        <v>4</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="H19" s="21">
+        <v>46108</v>
+      </c>
       <c r="I19" s="4"/>
       <c r="J19" s="4"/>
       <c r="K19" s="4"/>
@@ -4498,17 +4577,17 @@
       <c r="Y19" s="5"/>
       <c r="Z19" s="5"/>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A20" s="10">
-        <v>16</v>
+    <row r="20" spans="1:26" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A20" s="20">
+        <v>15</v>
       </c>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="14"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="21"/>
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
@@ -4528,17 +4607,17 @@
       <c r="Y20" s="5"/>
       <c r="Z20" s="5"/>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A21" s="10">
-        <v>17</v>
+    <row r="21" spans="1:26" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A21" s="20">
+        <v>16</v>
       </c>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="14"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="21"/>
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
@@ -4559,16 +4638,16 @@
       <c r="Z21" s="5"/>
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A22" s="10">
-        <v>18</v>
+      <c r="A22" s="20">
+        <v>17</v>
       </c>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="14"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="21"/>
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
@@ -4588,15 +4667,17 @@
       <c r="Y22" s="5"/>
       <c r="Z22" s="5"/>
     </row>
-    <row r="23" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
+    <row r="23" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A23" s="20">
+        <v>18</v>
+      </c>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="21"/>
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
@@ -31806,5 +31887,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="597" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Deliverables/Sprint/Soen 341 - agile planning.xlsx
+++ b/Deliverables/Sprint/Soen 341 - agile planning.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\louay\Desktop\LZJCO-SOEN341_Project_W26\Deliverables\Sprint\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91D59408-85C5-493E-BC55-01E936E30B93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF257F67-B064-4130-B2F5-89230348F3AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="71">
   <si>
     <t>Team LZJCO</t>
   </si>
@@ -230,12 +230,6 @@
     <t>System will prevent duplicate meal assignments in the same week</t>
   </si>
   <si>
-    <t>-Implement duplicate validation logic
--Check if recipe already exists in same week
--Prevent overwrite
--Display error message</t>
-  </si>
-  <si>
     <t>System will automatically test  every push and pull request made</t>
   </si>
   <si>
@@ -278,6 +272,25 @@
 -Include daily calorie limit in the user's profile preferences
 -Update recipe UI to include calories</t>
   </si>
+  <si>
+    <t>-Implement duplicate validation logic
+-Check if recipe already exists in same week
+-Prevent overwrite
+-Display error message
+-Write Unit Test for the isDuplicate() Method</t>
+  </si>
+  <si>
+    <t>Cedric
+Constance</t>
+  </si>
+  <si>
+    <t>User interface styling will be modular and easier to maintain</t>
+  </si>
+  <si>
+    <t>-Separate styling from WeeklyPlanner.html into WeeklyPlanner.css
+-Improve maintainability and readability of UI code
+-Allow easier future UI updates</t>
+  </si>
 </sst>
 </file>
 
@@ -287,7 +300,7 @@
     <numFmt numFmtId="164" formatCode="mmm\ d"/>
     <numFmt numFmtId="165" formatCode="mmmm\ d"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -344,8 +357,15 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -370,14 +390,8 @@
         <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -454,15 +468,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -477,11 +482,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -535,23 +566,51 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3794,7 +3853,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z994"/>
+  <dimension ref="A1:Z993"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="18.7109375" customWidth="1"/>
@@ -4302,7 +4361,7 @@
         <v>17</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G13" s="12" t="s">
         <v>51</v>
@@ -4346,7 +4405,7 @@
         <v>25</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G14" s="12" t="s">
         <v>52</v>
@@ -4373,7 +4432,7 @@
       <c r="Y14" s="5"/>
       <c r="Z14" s="5"/>
     </row>
-    <row r="15" spans="1:26" ht="94.5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" ht="126" x14ac:dyDescent="0.2">
       <c r="A15" s="10">
         <v>11</v>
       </c>
@@ -4381,7 +4440,7 @@
         <v>54</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D15" s="12">
         <v>2</v>
@@ -4390,10 +4449,10 @@
         <v>29</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="H15" s="14">
         <v>46102</v>
@@ -4422,10 +4481,10 @@
         <v>12</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D16" s="12">
         <v>5</v>
@@ -4434,10 +4493,10 @@
         <v>29</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H16" s="14">
         <v>46102</v>
@@ -4466,10 +4525,10 @@
         <v>13</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D17" s="12">
         <v>6</v>
@@ -4478,10 +4537,10 @@
         <v>29</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H17" s="14">
         <v>46102</v>
@@ -4505,15 +4564,31 @@
       <c r="Y17" s="5"/>
       <c r="Z17" s="5"/>
     </row>
-    <row r="18" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A18" s="19"/>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
+    <row r="18" spans="1:26" ht="115.5" x14ac:dyDescent="0.2">
+      <c r="A18" s="23">
+        <v>14</v>
+      </c>
+      <c r="B18" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="D18" s="23">
+        <v>4</v>
+      </c>
+      <c r="E18" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="H18" s="26">
+        <v>46108</v>
+      </c>
       <c r="I18" s="4"/>
       <c r="J18" s="4"/>
       <c r="K18" s="4"/>
@@ -4533,61 +4608,61 @@
       <c r="Y18" s="5"/>
       <c r="Z18" s="5"/>
     </row>
-    <row r="19" spans="1:26" ht="115.5" x14ac:dyDescent="0.2">
-      <c r="A19" s="20">
-        <v>14</v>
+    <row r="19" spans="1:26" s="35" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="22">
+        <v>15</v>
       </c>
-      <c r="B19" s="22" t="s">
-        <v>66</v>
+      <c r="B19" s="30" t="s">
+        <v>69</v>
       </c>
-      <c r="C19" s="25" t="s">
-        <v>67</v>
+      <c r="C19" s="29" t="s">
+        <v>70</v>
       </c>
-      <c r="D19" s="20">
-        <v>4</v>
+      <c r="D19" s="19">
+        <v>2</v>
       </c>
-      <c r="E19" s="22" t="s">
+      <c r="E19" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="F19" s="12" t="s">
+      <c r="F19" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="G19" s="12" t="s">
-        <v>65</v>
+      <c r="G19" s="21" t="s">
+        <v>51</v>
       </c>
-      <c r="H19" s="21">
+      <c r="H19" s="20">
         <v>46108</v>
       </c>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="4"/>
-      <c r="L19" s="4"/>
-      <c r="M19" s="4"/>
-      <c r="N19" s="4"/>
-      <c r="O19" s="4"/>
-      <c r="P19" s="4"/>
-      <c r="Q19" s="4"/>
-      <c r="R19" s="4"/>
-      <c r="S19" s="4"/>
-      <c r="T19" s="4"/>
-      <c r="U19" s="4"/>
-      <c r="V19" s="4"/>
-      <c r="W19" s="4"/>
-      <c r="X19" s="4"/>
-      <c r="Y19" s="5"/>
-      <c r="Z19" s="5"/>
-    </row>
-    <row r="20" spans="1:26" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A20" s="20">
-        <v>15</v>
+      <c r="I19" s="33"/>
+      <c r="J19" s="33"/>
+      <c r="K19" s="33"/>
+      <c r="L19" s="33"/>
+      <c r="M19" s="33"/>
+      <c r="N19" s="33"/>
+      <c r="O19" s="33"/>
+      <c r="P19" s="33"/>
+      <c r="Q19" s="33"/>
+      <c r="R19" s="33"/>
+      <c r="S19" s="33"/>
+      <c r="T19" s="33"/>
+      <c r="U19" s="33"/>
+      <c r="V19" s="33"/>
+      <c r="W19" s="33"/>
+      <c r="X19" s="33"/>
+      <c r="Y19" s="34"/>
+      <c r="Z19" s="34"/>
+    </row>
+    <row r="20" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A20" s="27">
+        <v>16</v>
       </c>
-      <c r="B20" s="20"/>
-      <c r="C20" s="24"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="21"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="27"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="27"/>
+      <c r="H20" s="28"/>
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
@@ -4607,17 +4682,17 @@
       <c r="Y20" s="5"/>
       <c r="Z20" s="5"/>
     </row>
-    <row r="21" spans="1:26" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A21" s="20">
-        <v>16</v>
+    <row r="21" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A21" s="19">
+        <v>17</v>
       </c>
-      <c r="B21" s="20"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="21"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="20"/>
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
@@ -4638,16 +4713,16 @@
       <c r="Z21" s="5"/>
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A22" s="20">
-        <v>17</v>
+      <c r="A22" s="19">
+        <v>18</v>
       </c>
-      <c r="B22" s="20"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="21"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="20"/>
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
@@ -4667,17 +4742,15 @@
       <c r="Y22" s="5"/>
       <c r="Z22" s="5"/>
     </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A23" s="20">
-        <v>18</v>
-      </c>
-      <c r="B23" s="20"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="21"/>
+    <row r="23" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A23" s="4"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
@@ -31774,30 +31847,30 @@
       <c r="Z990" s="5"/>
     </row>
     <row r="991" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A991" s="4"/>
-      <c r="B991" s="4"/>
-      <c r="C991" s="4"/>
-      <c r="D991" s="4"/>
-      <c r="E991" s="4"/>
-      <c r="F991" s="4"/>
-      <c r="G991" s="4"/>
-      <c r="H991" s="4"/>
-      <c r="I991" s="4"/>
-      <c r="J991" s="4"/>
-      <c r="K991" s="4"/>
-      <c r="L991" s="4"/>
-      <c r="M991" s="4"/>
-      <c r="N991" s="4"/>
-      <c r="O991" s="4"/>
-      <c r="P991" s="4"/>
-      <c r="Q991" s="4"/>
-      <c r="R991" s="4"/>
-      <c r="S991" s="4"/>
-      <c r="T991" s="4"/>
-      <c r="U991" s="4"/>
-      <c r="V991" s="4"/>
-      <c r="W991" s="4"/>
-      <c r="X991" s="4"/>
+      <c r="A991" s="5"/>
+      <c r="B991" s="5"/>
+      <c r="C991" s="5"/>
+      <c r="D991" s="5"/>
+      <c r="E991" s="5"/>
+      <c r="F991" s="5"/>
+      <c r="G991" s="5"/>
+      <c r="H991" s="5"/>
+      <c r="I991" s="5"/>
+      <c r="J991" s="5"/>
+      <c r="K991" s="5"/>
+      <c r="L991" s="5"/>
+      <c r="M991" s="5"/>
+      <c r="N991" s="5"/>
+      <c r="O991" s="5"/>
+      <c r="P991" s="5"/>
+      <c r="Q991" s="5"/>
+      <c r="R991" s="5"/>
+      <c r="S991" s="5"/>
+      <c r="T991" s="5"/>
+      <c r="U991" s="5"/>
+      <c r="V991" s="5"/>
+      <c r="W991" s="5"/>
+      <c r="X991" s="5"/>
       <c r="Y991" s="5"/>
       <c r="Z991" s="5"/>
     </row>
@@ -31857,34 +31930,6 @@
       <c r="Y993" s="5"/>
       <c r="Z993" s="5"/>
     </row>
-    <row r="994" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A994" s="5"/>
-      <c r="B994" s="5"/>
-      <c r="C994" s="5"/>
-      <c r="D994" s="5"/>
-      <c r="E994" s="5"/>
-      <c r="F994" s="5"/>
-      <c r="G994" s="5"/>
-      <c r="H994" s="5"/>
-      <c r="I994" s="5"/>
-      <c r="J994" s="5"/>
-      <c r="K994" s="5"/>
-      <c r="L994" s="5"/>
-      <c r="M994" s="5"/>
-      <c r="N994" s="5"/>
-      <c r="O994" s="5"/>
-      <c r="P994" s="5"/>
-      <c r="Q994" s="5"/>
-      <c r="R994" s="5"/>
-      <c r="S994" s="5"/>
-      <c r="T994" s="5"/>
-      <c r="U994" s="5"/>
-      <c r="V994" s="5"/>
-      <c r="W994" s="5"/>
-      <c r="X994" s="5"/>
-      <c r="Y994" s="5"/>
-      <c r="Z994" s="5"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="597" r:id="rId1"/>

--- a/Deliverables/Sprint/Soen 341 - agile planning.xlsx
+++ b/Deliverables/Sprint/Soen 341 - agile planning.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\louay\Desktop\LZJCO-SOEN341_Project_W26\Deliverables\Sprint\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB0A9A62-5C46-4D6F-826D-0454E23F56F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8DE2B6C-0231-47BE-B989-17911A11535F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="82">
   <si>
     <t>Team LZJCO</t>
   </si>
@@ -311,6 +311,24 @@
     <t>-Write unit test for all code
 -write at least 2 acceptance tests for all user stories</t>
   </si>
+  <si>
+    <t>Sprint 1</t>
+  </si>
+  <si>
+    <t>Sprint 2</t>
+  </si>
+  <si>
+    <t>Sprint 3</t>
+  </si>
+  <si>
+    <t>Sprint 4</t>
+  </si>
+  <si>
+    <t>Octav</t>
+  </si>
+  <si>
+    <t>Story Points per sprint</t>
+  </si>
 </sst>
 </file>
 
@@ -538,7 +556,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -642,6 +660,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4149,7 +4173,10 @@
       <c r="A7" s="14"/>
       <c r="B7" s="14"/>
       <c r="C7" s="14"/>
-      <c r="D7" s="15"/>
+      <c r="D7" s="15">
+        <f>SUM(D3:D6)</f>
+        <v>17</v>
+      </c>
       <c r="E7" s="15"/>
       <c r="F7" s="15"/>
       <c r="G7" s="15"/>
@@ -4309,7 +4336,10 @@
       <c r="A11" s="14"/>
       <c r="B11" s="14"/>
       <c r="C11" s="14"/>
-      <c r="D11" s="15"/>
+      <c r="D11" s="15">
+        <f>SUM(D8:D10)</f>
+        <v>15</v>
+      </c>
       <c r="E11" s="15"/>
       <c r="F11" s="15"/>
       <c r="G11" s="15"/>
@@ -4476,7 +4506,7 @@
         <v>67</v>
       </c>
       <c r="D15" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" s="11" t="s">
         <v>29</v>
@@ -4564,7 +4594,7 @@
         <v>63</v>
       </c>
       <c r="D17" s="11">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E17" s="11" t="s">
         <v>29</v>
@@ -4691,7 +4721,10 @@
       </c>
       <c r="B20" s="29"/>
       <c r="C20" s="33"/>
-      <c r="D20" s="29"/>
+      <c r="D20" s="29">
+        <f>SUM(D12:D19)</f>
+        <v>33</v>
+      </c>
       <c r="E20" s="29"/>
       <c r="F20" s="29"/>
       <c r="G20" s="29"/>
@@ -4896,12 +4929,14 @@
       <c r="F26" s="31"/>
       <c r="G26" s="31"/>
       <c r="H26" s="31"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
-      <c r="K26" s="4"/>
-      <c r="L26" s="4"/>
-      <c r="M26" s="4"/>
-      <c r="N26" s="4"/>
+      <c r="I26" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="J26" s="37"/>
+      <c r="K26" s="37"/>
+      <c r="L26" s="37"/>
+      <c r="M26" s="37"/>
+      <c r="N26" s="37"/>
       <c r="O26" s="4"/>
       <c r="P26" s="4"/>
       <c r="Q26" s="4"/>
@@ -4924,12 +4959,20 @@
       <c r="F27" s="31"/>
       <c r="G27" s="31"/>
       <c r="H27" s="31"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
-      <c r="K27" s="4"/>
-      <c r="L27" s="4"/>
-      <c r="M27" s="4"/>
-      <c r="N27" s="4"/>
+      <c r="I27" s="36"/>
+      <c r="J27" s="36" t="s">
+        <v>76</v>
+      </c>
+      <c r="K27" s="36" t="s">
+        <v>77</v>
+      </c>
+      <c r="L27" s="36" t="s">
+        <v>78</v>
+      </c>
+      <c r="M27" s="36" t="s">
+        <v>79</v>
+      </c>
+      <c r="N27" s="36"/>
       <c r="O27" s="4"/>
       <c r="P27" s="4"/>
       <c r="Q27" s="4"/>
@@ -4952,12 +4995,25 @@
       <c r="F28" s="31"/>
       <c r="G28" s="31"/>
       <c r="H28" s="31"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
-      <c r="K28" s="4"/>
-      <c r="L28" s="4"/>
-      <c r="M28" s="4"/>
-      <c r="N28" s="4"/>
+      <c r="I28" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="J28" s="36">
+        <v>4</v>
+      </c>
+      <c r="K28" s="36">
+        <v>3</v>
+      </c>
+      <c r="L28" s="36">
+        <v>8</v>
+      </c>
+      <c r="M28" s="36">
+        <v>1</v>
+      </c>
+      <c r="N28" s="36">
+        <f>SUM(J28:M28)</f>
+        <v>16</v>
+      </c>
       <c r="O28" s="4"/>
       <c r="P28" s="4"/>
       <c r="Q28" s="4"/>
@@ -4980,12 +5036,25 @@
       <c r="F29" s="31"/>
       <c r="G29" s="31"/>
       <c r="H29" s="31"/>
-      <c r="I29" s="4"/>
-      <c r="J29" s="4"/>
-      <c r="K29" s="4"/>
-      <c r="L29" s="4"/>
-      <c r="M29" s="4"/>
-      <c r="N29" s="4"/>
+      <c r="I29" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="J29" s="36">
+        <v>3</v>
+      </c>
+      <c r="K29" s="36">
+        <v>3</v>
+      </c>
+      <c r="L29" s="36">
+        <v>7</v>
+      </c>
+      <c r="M29" s="36">
+        <v>1</v>
+      </c>
+      <c r="N29" s="36">
+        <f t="shared" ref="N29:N32" si="0">SUM(J29:M29)</f>
+        <v>14</v>
+      </c>
       <c r="O29" s="4"/>
       <c r="P29" s="4"/>
       <c r="Q29" s="4"/>
@@ -5008,12 +5077,25 @@
       <c r="F30" s="31"/>
       <c r="G30" s="31"/>
       <c r="H30" s="31"/>
-      <c r="I30" s="4"/>
-      <c r="J30" s="4"/>
-      <c r="K30" s="4"/>
-      <c r="L30" s="4"/>
-      <c r="M30" s="4"/>
-      <c r="N30" s="4"/>
+      <c r="I30" s="36" t="s">
+        <v>80</v>
+      </c>
+      <c r="J30" s="36">
+        <v>4</v>
+      </c>
+      <c r="K30" s="36">
+        <v>3</v>
+      </c>
+      <c r="L30" s="36">
+        <v>6</v>
+      </c>
+      <c r="M30" s="36">
+        <v>1</v>
+      </c>
+      <c r="N30" s="36">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
       <c r="O30" s="4"/>
       <c r="P30" s="4"/>
       <c r="Q30" s="4"/>
@@ -5036,12 +5118,25 @@
       <c r="F31" s="31"/>
       <c r="G31" s="31"/>
       <c r="H31" s="31"/>
-      <c r="I31" s="4"/>
-      <c r="J31" s="4"/>
-      <c r="K31" s="4"/>
-      <c r="L31" s="4"/>
-      <c r="M31" s="4"/>
-      <c r="N31" s="4"/>
+      <c r="I31" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="J31" s="36">
+        <v>3</v>
+      </c>
+      <c r="K31" s="36">
+        <v>3</v>
+      </c>
+      <c r="L31" s="36">
+        <v>7</v>
+      </c>
+      <c r="M31" s="36">
+        <v>1</v>
+      </c>
+      <c r="N31" s="36">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
       <c r="O31" s="4"/>
       <c r="P31" s="4"/>
       <c r="Q31" s="4"/>
@@ -5064,12 +5159,25 @@
       <c r="F32" s="31"/>
       <c r="G32" s="31"/>
       <c r="H32" s="31"/>
-      <c r="I32" s="4"/>
-      <c r="J32" s="4"/>
-      <c r="K32" s="4"/>
-      <c r="L32" s="4"/>
-      <c r="M32" s="4"/>
-      <c r="N32" s="4"/>
+      <c r="I32" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="J32" s="36">
+        <v>3</v>
+      </c>
+      <c r="K32" s="36">
+        <v>3</v>
+      </c>
+      <c r="L32" s="36">
+        <v>5</v>
+      </c>
+      <c r="M32" s="36">
+        <v>5</v>
+      </c>
+      <c r="N32" s="36">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
       <c r="O32" s="4"/>
       <c r="P32" s="4"/>
       <c r="Q32" s="4"/>
@@ -5092,12 +5200,24 @@
       <c r="F33" s="31"/>
       <c r="G33" s="31"/>
       <c r="H33" s="31"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4"/>
-      <c r="K33" s="4"/>
-      <c r="L33" s="4"/>
-      <c r="M33" s="4"/>
-      <c r="N33" s="4"/>
+      <c r="I33" s="36"/>
+      <c r="J33" s="36">
+        <f>SUM(J28:J32)</f>
+        <v>17</v>
+      </c>
+      <c r="K33" s="36">
+        <f t="shared" ref="K33:M33" si="1">SUM(K28:K32)</f>
+        <v>15</v>
+      </c>
+      <c r="L33" s="36">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="M33" s="36">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="N33" s="36"/>
       <c r="O33" s="4"/>
       <c r="P33" s="4"/>
       <c r="Q33" s="4"/>
@@ -31992,6 +32112,9 @@
       <c r="Z993" s="5"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="I26:N26"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="597" r:id="rId1"/>
 </worksheet>
